--- a/data/contacts.xlsx
+++ b/data/contacts.xlsx
@@ -4117,6 +4117,3966 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-alabama</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kay Ivey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alabama</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Alabama</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-alaska</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Dunleavy</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alaska</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Alaska</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-american-samoa</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pula’ali’i Nikolao Pula</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">American Samoa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of American Samoa</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-arizona</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katie Hobbs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arizona</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Arizona</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-arkansas</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sarah Huckabee Sanders</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arkansas</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Arkansas</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-california</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gavin Newsom</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">California</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of California</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-colorado</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jared Polis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colorado</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Colorado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-connecticut</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ned Lamont</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connecticut</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Connecticut</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-delaware</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matt Meyer</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delaware</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Delaware</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-florida</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ron DeSantis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florida</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Florida</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-georgia</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brian Kemp</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Georgia</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Georgia</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-guam</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lou Leon Guerrero</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guam</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Guam</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-hawaii</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Josh Green</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hawaii</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Hawaii</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-idaho</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brad Little</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idaho</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Idaho</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-illinois</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JB Pritzker</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Illinois</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Illinois</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-indiana</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Braun</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indiana</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Indiana</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-iowa</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim Reynolds</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iowa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Iowa</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-kansas</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laura Kelly</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kansas</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Kansas</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-kentucky</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andy Beshear</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kentucky</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Kentucky</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-louisiana</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeff Landry</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Louisiana</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Louisiana</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-maine</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Janet Mills</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maine</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Maine</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-maryland</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wes Moore</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maryland</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Maryland</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-massachusetts</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maura Healey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Massachusetts</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Massachusetts</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-michigan</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gretchen Whitmer</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michigan</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Michigan</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-minnesota</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tim Walz</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minnesota</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Minnesota</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-mississippi</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tate Reeves</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mississippi</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Mississippi</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-missouri</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Kehoe</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Missouri</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Missouri</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-montana</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greg Gianforte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montana</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Montana</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-nebraska</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jim Pillen</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nebraska</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Nebraska</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-nevada</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joe Lombardo</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nevada</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Nevada</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-new-hampshire</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kelly Ayotte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Hampshire</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of New Hampshire</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-new-jersey</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mikie Sherrill</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Jersey</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of New Jersey</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-new-mexico</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michelle Lujan Grisham</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Mexico</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of New Mexico</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-new-york</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kathy Hochul</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New York</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of New York</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-north-carolina</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Josh Stein</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North Carolina</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of North Carolina</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-north-dakota</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kelly Armstrong</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North Dakota</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of North Dakota</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-northern-mariana-islands</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">David M. Apatang</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northern Mariana Islands</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Northern Mariana Islands</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-ohio</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike DeWine</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ohio</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Ohio</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-oklahoma</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kevin Stitt</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oklahoma</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Oklahoma</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-oregon</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tina Kotek</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oregon</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Oregon</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-pennsylvania</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Josh Shapiro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pennsylvania</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Pennsylvania</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-puerto-rico</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jenniffer González-Colón</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puerto Rico</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Puerto Rico</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-rhode-island</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dan McKee</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rhode Island</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Rhode Island</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-south-carolina</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henry McMaster</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South Carolina</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of South Carolina</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-south-dakota</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Larry Rhoden</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South Dakota</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of South Dakota</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-tennessee</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill Lee</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tennessee</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Tennessee</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-texas</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greg Abbott</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texas</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Texas</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-utah</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spencer Cox</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utah</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Utah</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-vermont</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phil Scott</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vermont</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Vermont</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-u-s--virgin-islands</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Albert Bryan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U.S. Virgin Islands</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of U.S. Virgin Islands</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-virginia</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abigail Spanberger</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Virginia</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Virginia</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-washington</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bob Ferguson</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Washington</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Washington</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-west-virginia</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick Morrisey</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">West Virginia</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of West Virginia</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-wisconsin</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tony Evers</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wisconsin</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Wisconsin</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor-wyoming</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mark Gordon</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wyoming</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office of the Governor of Wyoming</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_review</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4215,6 +8175,2866 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alabama</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alaska</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">American Samoa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arizona</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arkansas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">California</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colorado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connecticut</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delaware</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Georgia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guam</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hawaii</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idaho</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Illinois</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indiana</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iowa</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kansas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kentucky</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Louisiana</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maine</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maryland</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Massachusetts</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michigan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minnesota</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mississippi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Missouri</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montana</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nebraska</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nevada</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Hampshire</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Jersey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Mexico</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New York</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North Carolina</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North Dakota</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Northern Mariana Islands</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ohio</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oklahoma</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oregon</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rhode Island</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South Carolina</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South Dakota</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tennessee</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texas</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utah</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vermont</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U.S. Virgin Islands</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Virginia</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Washington</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">West Virginia</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wisconsin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">state_territory</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wyoming</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">in_progress</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/data/contacts.xlsx
+++ b/data/contacts.xlsx
@@ -4175,7 +4175,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.alabama.gov/contact/</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.alaska.gov/contact/</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.americansamoa.gov/governorpulaalii</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://azgovernor.gov/contact</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.arkansas.gov/contact-the-governor/</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.gov.ca.gov/contact/</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Governorpolis@state.co.us</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governorsoffice.colorado.gov/governor/contact-us</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://portal.ct.gov/governor/contact/email-governor-lamont</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.delaware.gov/contact-the-governors-office/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.flgov.com/contact-governor/</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.georgia.gov/contact-us</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.guam.gov/contact-us/</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.hawaii.gov/contact-us/</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.idaho.gov/contact-us/</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.illinois.gov/contact-us/</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.in.gov/gov/contact/</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.iowa.gov/contact</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.kansas.gov/contact/</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.ky.gov/contact</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.louisiana.gov/page/contact</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.maine.gov/governor/mills/contact</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.maryland.gov/leadership/governor-wes-moore</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.mass.gov/info-details/email-the-governors-office</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.michigan.gov/whitmer/contact</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://mn.gov/governor/contact/</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governorreeves.ms.gov/contact/</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.mo.gov/contact-us</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.mt.gov/Contact/default</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.nebraska.gov/contact-form</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.nv.gov/Contact/Contact_Us/</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.nh.gov/contact-us</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.nj.gov/governor/contact/</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.state.nm.us/contact-the-governor/</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.ny.gov/content/governor-contact-form</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.nc.gov/contact</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.nd.gov/contact-us</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.cnmi.gov/contact/</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.ohio.gov/contact</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://oklahoma.gov/governor/contact.html</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.oregon.gov/gov/Pages/share-your-opinion.aspx</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.pa.gov/contact/</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.fortaleza.pr.gov/</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.ri.gov/contact-us</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.sc.gov/contact-office-governor</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.sd.gov/contact.aspx</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.tn.gov/governor/contact-us.html</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.texas.gov/contact</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.utah.gov/contact/</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.vermont.gov/contact-us</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.vi.gov/governor-bryan/</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.virginia.gov/constituent-services/contact-the-governor/</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.wa.gov/contacting-governor/contacting-governors-office</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.wv.gov/Pages/Contact.aspx</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://evers.wi.gov/pages/connect.aspx</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.wyo.gov/contact</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8208,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.alabama.gov/contact/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора. Связь через веб-форму и приёмную; прямой публичный email и LinkedIn не публикуются.</t>
         </is>
       </c>
     </row>
@@ -8260,12 +8260,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.alaska.gov/contact/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора. Связь через официальную форму обращений; прямой email и LinkedIn не публикуются.</t>
         </is>
       </c>
     </row>
@@ -8312,12 +8312,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.americansamoa.gov/governorpulaalii</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный правительственный портал Американского Самоа. Связь через аппарат губернатора; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://azgovernor.gov/contact</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт офиса губернатора. Связь через защищённую форму обращений граждан; прямой email и LinkedIn не публикуются.</t>
         </is>
       </c>
     </row>
@@ -8416,12 +8416,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.arkansas.gov/contact-the-governor/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора. Связь через веб-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.gov.ca.gov/contact/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Калифорнии. Связь через онлайн-форму приёмной; прямой email и личный LinkedIn не публикуются.</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governorsoffice.colorado.gov/governor/contact-us</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал офиса губернатора. Опубликован официальный служебный адрес электронной почты Governorpolis@state.co.us.</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://portal.ct.gov/governor/contact/email-governor-lamont</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал штата Коннектикут. Связь через форму обращений граждан; прямой публичный email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8624,12 +8624,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.delaware.gov/contact-the-governors-office/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Делавэра. Связь через форму обращений и телефонную линию; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.flgov.com/contact-governor/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал Executive Office of the Governor. Связь через контактную форму; прямой публичный email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8728,12 +8728,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.georgia.gov/contact-us</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Джорджии. Связь через форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.guam.gov/contact-us/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт офиса губернатора Гуама. Связь через контактную страницу и приёмную; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.hawaii.gov/contact-us/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Гавайев. Связь через веб-форму и канцелярию; прямой публичный email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.idaho.gov/contact-us/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Айдахо. Связь через форму обращения граждан; прямой подтверждённый email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.illinois.gov/contact-us/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Иллинойса. Связь через веб-форму обращений; прямой публичный email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -8988,12 +8988,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.in.gov/gov/contact/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Индианы. Связь через защищённую онлайн-форму IN.gov; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9040,12 +9040,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.iowa.gov/contact</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Айовы. Связь через онлайн-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.kansas.gov/contact/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Канзаса. Связь через портал обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.ky.gov/contact</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Кентукки. Связь через форму обращений граждан; прямой публичный email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9196,12 +9196,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.louisiana.gov/page/contact</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт офиса губернатора Луизианы. Связь через контактную веб-форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9248,12 +9248,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.maine.gov/governor/mills/contact</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора штата Мэн. Связь через онлайн-форму обращений граждан; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9300,12 +9300,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.maryland.gov/leadership/governor-wes-moore</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Мэриленда. Связь через канцелярию и веб-портал; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9352,12 +9352,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.mass.gov/info-details/email-the-governors-office</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал Содружества Массачусетс. Связь через форму Email the Governor Office; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9404,12 +9404,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.michigan.gov/whitmer/contact</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Мичигана. Связь через форму службы поддержки граждан; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9456,12 +9456,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://mn.gov/governor/contact/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Миннесоты. Связь через онлайн-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9508,12 +9508,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governorreeves.ms.gov/contact/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Миссисипи. Связь через контактную форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.mo.gov/contact-us</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Миссури. Связь через контактную онлайн-форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9612,12 +9612,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.mt.gov/Contact/default</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Монтаны. Связь через веб-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9664,12 +9664,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.nebraska.gov/contact-form</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Небраски. Связь через форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.nv.gov/Contact/Contact_Us/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Невады. Связь через контактную форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9768,12 +9768,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.nh.gov/contact-us</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Нью-Гэмпшира. Связь через веб-форму и канцелярию; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9820,12 +9820,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.nj.gov/governor/contact/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Нью-Джерси. Связь через онлайн-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9872,12 +9872,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.state.nm.us/contact-the-governor/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Нью-Мексико. Связь через форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9924,12 +9924,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.ny.gov/content/governor-contact-form</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Нью-Йорка. Связь через электронную контактную форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.nc.gov/contact</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Северной Каролины. Связь через контактную веб-форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10028,12 +10028,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.nd.gov/contact-us</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Северной Дакоты. Связь через контактную форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10080,12 +10080,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.cnmi.gov/contact/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора СМОИ. Связь через контактную форму и канцелярию; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10132,12 +10132,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.ohio.gov/contact</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Огайо. Связь через веб-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10184,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://oklahoma.gov/governor/contact.html</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал штата Оклахома. Связь через контактную форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.oregon.gov/gov/Pages/share-your-opinion.aspx</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Орегона. Связь через веб-форму обращений граждан; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.pa.gov/contact/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Пенсильвании. Связь через онлайн-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10340,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.fortaleza.pr.gov/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал администрации губернатора Пуэрто-Рико (La Fortaleza). Связь через канцелярию; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.ri.gov/contact-us</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Род-Айленда. Связь через онлайн-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10444,12 +10444,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.sc.gov/contact-office-governor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Южной Каролины. Связь через форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10496,12 +10496,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.sd.gov/contact.aspx</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Южной Дакоты. Связь через веб-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.tn.gov/governor/contact-us.html</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал штата Теннесси. Связь через форму Share My Opinion; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10600,12 +10600,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://gov.texas.gov/contact</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Техаса. Связь через защищённую контактную форму и телефонные линии; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10652,12 +10652,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.utah.gov/contact/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Юты. Связь через форму обращений граждан; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10704,12 +10704,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.vermont.gov/contact-us</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Вермонта. Связь через онлайн-форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10756,12 +10756,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.vi.gov/governor-bryan/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал правительства Американских Виргинских Островов. Связь через канцелярию губернатора; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10808,12 +10808,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://www.governor.virginia.gov/constituent-services/contact-the-governor/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Виргинии. Связь через портал Constituent Services; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10860,12 +10860,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.wa.gov/contacting-governor/contacting-governors-office</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Вашингтона. Связь через электронную форму обращений; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10912,12 +10912,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.wv.gov/Pages/Contact.aspx</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Западной Виргинии. Связь через контактную веб-форму; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://evers.wi.gov/pages/connect.aspx</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный сайт губернатора Висконсина. Связь через портал Connect with the Governor; прямой email не публикуется.</t>
         </is>
       </c>
     </row>
@@ -11016,12 +11016,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_progress</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.nga.org/Governors/</t>
+          <t xml:space="preserve">https://governor.wyo.gov/contact</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имя взято из текущего списка NGA; служебная почта и LinkedIn требуют отдельной проверки.</t>
+          <t xml:space="preserve">Официальный портал губернатора Вайоминга. Связь через форму обращений и телефонную связь; прямой email не публикуется.</t>
         </is>
       </c>
     </row>

--- a/data/contacts.xlsx
+++ b/data/contacts.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign Affairs Officer/FDI Manager</t>
+          <t xml:space="preserve">Foreign Affairs Officer/FDI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -153,7 +153,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.trade.gov/selectusa-find-economic-developers</t>
+          <t xml:space="preserve">https://www.madeinalabama.com/resources/contacts/gary-walton/</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -163,7 +163,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director of Business Attraction</t>
+          <t xml:space="preserve">Vice President of International Business Attraction</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Office of the Deputy Mayor for Planning and Economic Development</t>
+          <t xml:space="preserve">Washington DC Economic Partnership</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.trade.gov/selectusa-find-economic-developers</t>
+          <t xml:space="preserve">https://wdcep.com/team/</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_review</t>
+          <t xml:space="preserve">verified</t>
         </is>
       </c>
     </row>
